--- a/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-05_Accounting_Disbursement_ACSL_Vol1_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-05_Accounting_Disbursement_ACSL_Vol1_v1.0.xlsx
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and demo user for built BRDs)</t>
+          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Demo seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Demo users of TD-AC-01.</t>
+          <t>SIT/UAT users of TD-AC-01.</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Demo chart TD-AC-02; upload file TD-AC-04; rates TD-AC-03.</t>
+          <t>Seed chart TD-AC-02; upload file TD-AC-04; rates TD-AC-03.</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Posted demo journals of the current year.</t>
+          <t>Posted seed journals of the current year.</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Posted demo data of the current year.</t>
+          <t>Posted seed data of the current year.</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-01 Demo users and roles</t>
+          <t>Data: TD-AC-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-01 Demo users and roles</t>
+          <t>Data: TD-AC-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-01 Demo users and roles</t>
+          <t>Data: TD-AC-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-01 Demo users and roles</t>
+          <t>Data: TD-AC-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-02 Demo chart and posting rules</t>
+          <t>Data: TD-AC-02 Seed chart and posting rules</t>
         </is>
       </c>
       <c r="J18" s="12" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-02 Demo chart and posting rules</t>
+          <t>Data: TD-AC-02 Seed chart and posting rules</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-02 Demo chart and posting rules</t>
+          <t>Data: TD-AC-02 Seed chart and posting rules</t>
         </is>
       </c>
       <c r="J20" s="12" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-02 Demo chart and posting rules</t>
+          <t>Data: TD-AC-02 Seed chart and posting rules</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-02 Demo chart and posting rules</t>
+          <t>Data: TD-AC-02 Seed chart and posting rules</t>
         </is>
       </c>
       <c r="J22" s="12" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-02 Demo chart and posting rules</t>
+          <t>Data: TD-AC-02 Seed chart and posting rules</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-02 Demo chart and posting rules</t>
+          <t>Data: TD-AC-02 Seed chart and posting rules</t>
         </is>
       </c>
       <c r="J24" s="12" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>GlPlatformApiIT#chartUploadDemoFileLoadsPendingAuthorization</t>
+          <t>GlPlatformApiIT#chartUploadSeedFileLoadsPendingAuthorization</t>
         </is>
       </c>
       <c r="N25" s="27" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="M37" s="12" t="inlineStr">
         <is>
-          <t>GlPlatformApiIT#chartUploadDemoFileLoadsPendingAuthorization</t>
+          <t>GlPlatformApiIT#chartUploadSeedFileLoadsPendingAuthorization</t>
         </is>
       </c>
       <c r="N37" s="27" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H50" s="12" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H53" s="12" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-02 Demo chart and posting rules</t>
+          <t>Data: TD-AC-02 Seed chart and posting rules</t>
         </is>
       </c>
       <c r="J55" s="12" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
@@ -10774,7 +10774,7 @@
       <c r="I56" s="12" t="inlineStr">
         <is>
           <t>The test lead deactivates the rule of an event type used in the test (for example FRBS_SERVICE_FEE_ACCRUE).
-Data: TD-AC-02 Demo chart and posting rules</t>
+Data: TD-AC-02 Seed chart and posting rules</t>
         </is>
       </c>
       <c r="J56" s="12" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-02 Demo chart and posting rules</t>
+          <t>Data: TD-AC-02 Seed chart and posting rules</t>
         </is>
       </c>
       <c r="J57" s="12" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-02 Demo chart and posting rules</t>
+          <t>Data: TD-AC-02 Seed chart and posting rules</t>
         </is>
       </c>
       <c r="J58" s="12" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-02 Demo chart and posting rules</t>
+          <t>Data: TD-AC-02 Seed chart and posting rules</t>
         </is>
       </c>
       <c r="J59" s="12" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H65" s="12" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H67" s="12" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H68" s="12" t="inlineStr">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H70" s="12" t="inlineStr">
@@ -11892,7 +11892,7 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H72" s="12" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H73" s="12" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H74" s="12" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H75" s="12" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H77" s="12" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H78" s="12" t="inlineStr">
@@ -12490,7 +12490,7 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H80" s="12" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H81" s="12" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H82" s="12" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H83" s="12" t="inlineStr">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H84" s="12" t="inlineStr">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H86" s="12" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H87" s="12" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="H89" s="12" t="inlineStr">
@@ -13294,7 +13294,7 @@
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H90" s="12" t="inlineStr">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H91" s="12" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H92" s="12" t="inlineStr">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H93" s="12" t="inlineStr">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H94" s="12" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H95" s="12" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H96" s="12" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H97" s="12" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H98" s="12" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H100" s="12" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H101" s="12" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H102" s="12" t="inlineStr">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H103" s="12" t="inlineStr">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H104" s="12" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H105" s="12" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H106" s="12" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H107" s="12" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H108" s="12" t="inlineStr">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H109" s="12" t="inlineStr">
@@ -14735,7 +14735,7 @@
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H110" s="12" t="inlineStr">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H111" s="12" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H112" s="12" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H113" s="12" t="inlineStr">
@@ -15034,7 +15034,7 @@
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H114" s="12" t="inlineStr">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H115" s="12" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H116" s="12" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H118" s="12" t="inlineStr">
@@ -15343,7 +15343,7 @@
       <c r="I118" s="12" t="inlineStr">
         <is>
           <t>A CBG invoice fully paid in the period with commission 10,000.00 and insurer WTAX 200.00.
-Data: TD-AC-06 Service fee rules and demo run</t>
+Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J118" s="12" t="inlineStr">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H119" s="12" t="inlineStr">
@@ -15419,7 +15419,7 @@
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J119" s="12" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H120" s="12" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="I120" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J120" s="12" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H121" s="12" t="inlineStr">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J121" s="12" t="inlineStr">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H122" s="12" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="I122" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J122" s="12" t="inlineStr">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H123" s="12" t="inlineStr">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H124" s="12" t="inlineStr">
@@ -15802,7 +15802,7 @@
       </c>
       <c r="I124" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J124" s="12" t="inlineStr">
@@ -15865,7 +15865,7 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H125" s="12" t="inlineStr">
@@ -15875,7 +15875,7 @@
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J125" s="12" t="inlineStr">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H126" s="12" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="I126" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J126" s="12" t="inlineStr">
@@ -16015,7 +16015,7 @@
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H127" s="12" t="inlineStr">
@@ -16025,7 +16025,7 @@
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J127" s="12" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H128" s="12" t="inlineStr">
@@ -16098,12 +16098,12 @@
       </c>
       <c r="I128" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J128" s="12" t="inlineStr">
         <is>
-          <t>1. Ask Disbursement to pay a line of the demo run on 5 September.
+          <t>1. Ask Disbursement to pay a line of the seed run on 5 September.
 2. Open the run.</t>
         </is>
       </c>
@@ -16165,7 +16165,7 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H129" s="12" t="inlineStr">
@@ -16175,7 +16175,7 @@
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H130" s="12" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="I130" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J130" s="12" t="inlineStr">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H131" s="12" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J131" s="12" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H132" s="12" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="I132" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J132" s="12" t="inlineStr">
@@ -16460,7 +16460,7 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J133" s="12" t="inlineStr">
@@ -16537,7 +16537,7 @@
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H134" s="12" t="inlineStr">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="I134" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J134" s="12" t="inlineStr">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H135" s="12" t="inlineStr">
@@ -16624,7 +16624,7 @@
       <c r="I135" s="12" t="inlineStr">
         <is>
           <t>The test lead deactivates the 5614 rule.
-Data: TD-AC-06 Service fee rules and demo run</t>
+Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J135" s="12" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H136" s="12" t="inlineStr">
@@ -16702,7 +16702,7 @@
       </c>
       <c r="I136" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-AC-06 Service fee rules and demo run</t>
+          <t>Data: TD-AC-06 Service fee rules and seed run</t>
         </is>
       </c>
       <c r="J136" s="12" t="inlineStr">
@@ -16769,7 +16769,7 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H138" s="12" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H140" s="12" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H142" s="12" t="inlineStr">
@@ -17194,7 +17194,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H144" s="12" t="inlineStr">
@@ -17338,7 +17338,7 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H145" s="12" t="inlineStr">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H146" s="12" t="inlineStr">
@@ -17484,7 +17484,7 @@
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H147" s="12" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H148" s="12" t="inlineStr">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H149" s="12" t="inlineStr">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="H150" s="12" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H151" s="12" t="inlineStr">
@@ -17836,7 +17836,7 @@
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H152" s="12" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H153" s="12" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H154" s="12" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H155" s="12" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H156" s="12" t="inlineStr">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H157" s="12" t="inlineStr">
@@ -18256,7 +18256,7 @@
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H158" s="12" t="inlineStr">
@@ -18329,7 +18329,7 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H159" s="12" t="inlineStr">
@@ -18398,7 +18398,7 @@
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="H160" s="12" t="inlineStr">
@@ -18467,7 +18467,7 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr">
@@ -18539,7 +18539,7 @@
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H162" s="12" t="inlineStr">
@@ -18616,7 +18616,7 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H163" s="12" t="inlineStr">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H164" s="12" t="inlineStr">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H165" s="12" t="inlineStr">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H166" s="12" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H167" s="12" t="inlineStr">
@@ -18998,7 +18998,7 @@
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H168" s="12" t="inlineStr">
@@ -19029,7 +19029,7 @@
       </c>
       <c r="M168" s="12" t="inlineStr">
         <is>
-          <t>AccessRequestIT#requestsAreValidatedAndDecidedUnderFourEyes; accessRequest.test.ts#needs a new user name, full name, roles and justification to create a user</t>
+          <t>AccessRequestIT#requestsAreValidatedAndDecidedUnderFourEyes; accessRequest.test.ts#needs the new user data, a group profile, the remarks and the approver to submit</t>
         </is>
       </c>
       <c r="N168" s="27" t="inlineStr">
@@ -19075,7 +19075,7 @@
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H169" s="12" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H170" s="12" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H171" s="12" t="inlineStr">
@@ -19294,7 +19294,7 @@
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H172" s="12" t="inlineStr">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H173" s="12" t="inlineStr">
@@ -19440,7 +19440,7 @@
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H174" s="12" t="inlineStr">
@@ -19517,7 +19517,7 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>ACCESS_APPROVER – Access approver (ACCESS_APPROVE) (demo user approver)</t>
+          <t>ACCESS_APPROVER – Access approver (ACCESS_APPROVE) (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="H175" s="12" t="inlineStr">
@@ -19593,7 +19593,7 @@
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
-          <t>ACCESS_APPROVER – Access approver (ACCESS_APPROVE) (demo user approver)</t>
+          <t>ACCESS_APPROVER – Access approver (ACCESS_APPROVE) (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="H176" s="12" t="inlineStr">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>ACCESS_APPROVER – Access approver (ACCESS_APPROVE) (demo user approver)</t>
+          <t>ACCESS_APPROVER – Access approver (ACCESS_APPROVE) (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="H177" s="12" t="inlineStr">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
-          <t>ACCESS_APPROVER – Access approver (ACCESS_APPROVE) (demo user approver)</t>
+          <t>ACCESS_APPROVER – Access approver (ACCESS_APPROVE) (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="H178" s="12" t="inlineStr">
@@ -19816,7 +19816,7 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H179" s="12" t="inlineStr">
@@ -19889,7 +19889,7 @@
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H180" s="12" t="inlineStr">
@@ -19967,7 +19967,7 @@
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>ACCESS_APPROVER – Access approver (ACCESS_APPROVE) (demo user approver)</t>
+          <t>ACCESS_APPROVER – Access approver (ACCESS_APPROVE) (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="H181" s="12" t="inlineStr">
@@ -20040,7 +20040,7 @@
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
-          <t>ACCESS_APPROVER – Access approver (ACCESS_APPROVE) (demo user approver)</t>
+          <t>ACCESS_APPROVER – Access approver (ACCESS_APPROVE) (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="H182" s="12" t="inlineStr">
@@ -25266,17 +25266,17 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Demo users and roles</t>
+          <t>SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>glofficer (FRBS_PROCESSOR), gltl (FRBS_TL), glhead (FRBS_HEAD), badmin (BUSINESS_ADMIN), admin (SYSADMIN), approver (NB_APPROVER, holds ACCESS_APPROVE), comptrol (COMPTROLLERSHIP), auditor (AUDITOR), disb (DISBURSEMENT), remittl (REMIT_TL). The demo password is issued by the test lead.</t>
+          <t>glofficer (FRBS_PROCESSOR), gltl (FRBS_TL), glhead (FRBS_HEAD), badmin (BUSINESS_ADMIN), admin (SYSADMIN), approver (NB_APPROVER, holds ACCESS_APPROVE), comptrol (COMPTROLLERSHIP), auditor (AUDITOR), disb (DISBURSEMENT), remittl (REMIT_TL). The SIT/UAT password is issued by the test lead.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Demo seeds V999 (BRD-5 users), V980, V990, V900; grants V890 and V899</t>
+          <t>Seeds V999 (BRD-5 users), V980, V990, V900; grants V890 and V899</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -25291,17 +25291,17 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Demo chart and posting rules</t>
+          <t>Seed chart and posting rules</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Demo chart of company FVI (placeholder for BDOI's chart, AQ01) with 1210 premium receivable, 2211 due to insurer, 2241 checks outstanding, 2250 service fee payable, 4130 incentive income, 4131 CPC2 income, 5614 service fee expense (cost centre required); demo accounting rules of the BRD-5 events</t>
+          <t>Seed chart of company FVI (placeholder for BDOI's chart, AQ01) with 1210 premium receivable, 2211 due to insurer, 2241 checks outstanding, 2250 service fee payable, 4130 incentive income, 4131 CPC2 income, 5614 service fee expense (cost centre required); seed accounting rules of the BRD-5 events</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Demo seeds V900, V901 and V999</t>
+          <t>Seeds V900, V901 and V999</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
@@ -25326,7 +25326,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V900 and the currency master</t>
+          <t>Seed V900 and the currency master</t>
         </is>
       </c>
       <c r="E7" s="12" t="n">
@@ -25391,7 +25391,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Service fee rules and demo run</t>
+          <t>Service fee rules and seed run</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Migration V898 and demo runner FrbsDemoData</t>
+          <t>Migration V898 and seed runner FrbsSeedData</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
@@ -25421,12 +25421,12 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>The statement layout of a demo bank account; a CSV bank file with check 000123 for 15,000.00 dated two days after the book payment of check 000123, and a deposit in transit left unmatched</t>
+          <t>The statement layout of a seed bank account; a CSV bank file with check 000123 for 15,000.00 dated two days after the book payment of check 000123, and a deposit in transit left unmatched</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Receivables demo (ReceivablesDemoData) and a file prepared by the test lead</t>
+          <t>Receivables seed (ReceivablesSeedData) and a file prepared by the test lead</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
@@ -25625,7 +25625,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -25676,7 +25676,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -25727,7 +25727,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -25778,7 +25778,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -25829,7 +25829,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -25880,7 +25880,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -25927,7 +25927,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -25974,7 +25974,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -26021,7 +26021,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -26068,7 +26068,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -26115,7 +26115,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -26162,7 +26162,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -26209,7 +26209,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -26256,7 +26256,7 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -26350,7 +26350,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -26401,7 +26401,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -26452,7 +26452,7 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -26503,7 +26503,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -26554,7 +26554,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -26605,7 +26605,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -26656,7 +26656,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -26703,7 +26703,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -26750,7 +26750,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -26797,7 +26797,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -26899,7 +26899,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -26950,7 +26950,7 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -27001,7 +27001,7 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -27048,7 +27048,7 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -27095,7 +27095,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -27142,7 +27142,7 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -27193,7 +27193,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -27295,7 +27295,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -27346,7 +27346,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -27397,7 +27397,7 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -27448,7 +27448,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -27499,7 +27499,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -27550,7 +27550,7 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -27601,7 +27601,7 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -27703,7 +27703,7 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -27754,7 +27754,7 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -27805,7 +27805,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -27856,7 +27856,7 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (demo user glofficer)</t>
+          <t>FRBS_PROCESSOR – GL Officer (FRBS Processor) (SIT/UAT user glofficer)</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -27903,7 +27903,7 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -27950,7 +27950,7 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -27997,7 +27997,7 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -28044,7 +28044,7 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -28091,7 +28091,7 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -28138,7 +28138,7 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>FRBS_TL – GL Team Lead (demo user gltl)</t>
+          <t>FRBS_TL – GL Team Lead (SIT/UAT user gltl)</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -28185,7 +28185,7 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -28232,7 +28232,7 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -28279,7 +28279,7 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -28330,7 +28330,7 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
@@ -28381,7 +28381,7 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -28432,7 +28432,7 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
@@ -28483,7 +28483,7 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>ACCESS_APPROVER – Access approver (ACCESS_APPROVE) (demo user approver)</t>
+          <t>ACCESS_APPROVER – Access approver (ACCESS_APPROVE) (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -28534,7 +28534,7 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -28585,7 +28585,7 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -28636,7 +28636,7 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>FRBS_HEAD – GL Team Head / Section Head (demo user glhead)</t>
+          <t>FRBS_HEAD – GL Team Head / Section Head (SIT/UAT user glhead)</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
